--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB8B738-F043-4148-8F19-12A96A1B743C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF10C83A-068B-4BB8-83C5-4166A6CDE4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -572,16 +572,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>385</v>
+        <v>499</v>
       </c>
       <c r="C2" s="4">
-        <v>518</v>
+        <v>826</v>
       </c>
       <c r="D2" s="9">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E2" s="13">
-        <v>2.3333333333333335</v>
+        <v>2.5</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -591,16 +591,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="C3" s="4">
-        <v>627</v>
+        <v>1018</v>
       </c>
       <c r="D3" s="9">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E3" s="13">
-        <v>2.3333333333333335</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,16 +610,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c r="C4" s="4">
-        <v>602</v>
+        <v>986</v>
       </c>
       <c r="D4" s="9">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E4" s="13">
-        <v>2.2222222222222223</v>
+        <v>2.3571428571428572</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,16 +629,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="C5" s="4">
-        <v>502</v>
+        <v>830</v>
       </c>
       <c r="D5" s="9">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E5" s="13">
-        <v>2</v>
+        <v>2.0714285714285716</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -648,16 +648,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="C6" s="4">
-        <v>477</v>
+        <v>957</v>
       </c>
       <c r="D6" s="9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="13">
-        <v>3.5555555555555554</v>
+        <v>2.4285714285714284</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,16 +667,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="C7" s="4">
-        <v>523</v>
+        <v>932</v>
       </c>
       <c r="D7" s="9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" s="13">
-        <v>3.6666666666666665</v>
+        <v>2.2142857142857144</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -686,16 +686,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="C8" s="4">
-        <v>480</v>
+        <v>747</v>
       </c>
       <c r="D8" s="9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E8" s="13">
-        <v>1.6666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,16 +705,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="C9" s="4">
-        <v>705</v>
+        <v>1053</v>
       </c>
       <c r="D9" s="9">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E9" s="13">
-        <v>2.2222222222222223</v>
+        <v>2.5714285714285716</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,16 +724,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="C10" s="4">
-        <v>464</v>
+        <v>705</v>
       </c>
       <c r="D10" s="9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E10" s="13">
-        <v>2.2222222222222223</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,16 +743,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="C11" s="4">
-        <v>605</v>
+        <v>995</v>
       </c>
       <c r="D11" s="9">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E11" s="13">
-        <v>2.8888888888888888</v>
+        <v>3.3571428571428572</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,16 +762,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>197</v>
+        <v>337</v>
       </c>
       <c r="C12" s="4">
-        <v>399</v>
+        <v>800</v>
       </c>
       <c r="D12" s="9">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E12" s="13">
-        <v>2.6666666666666665</v>
+        <v>2.7857142857142856</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -781,16 +781,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="C13" s="4">
-        <v>530</v>
+        <v>888</v>
       </c>
       <c r="D13" s="9">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E13" s="13">
-        <v>2.8888888888888888</v>
+        <v>2.8571428571428572</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,16 +800,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C14" s="4">
-        <v>491</v>
+        <v>685</v>
       </c>
       <c r="D14" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" s="13">
-        <v>2.1111111111111112</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,16 +819,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C15" s="4">
-        <v>653</v>
+        <v>890</v>
       </c>
       <c r="D15" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" s="13">
-        <v>2.1111111111111112</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -838,16 +838,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="C16" s="4">
-        <v>433</v>
+        <v>899</v>
       </c>
       <c r="D16" s="9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E16" s="13">
-        <v>3.1111111111111112</v>
+        <v>2.7142857142857144</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -857,16 +857,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>243</v>
+        <v>313</v>
       </c>
       <c r="C17" s="4">
-        <v>693</v>
+        <v>932</v>
       </c>
       <c r="D17" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E17" s="13">
-        <v>1.5555555555555556</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -876,16 +876,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="C18" s="4">
-        <v>403</v>
+        <v>945</v>
       </c>
       <c r="D18" s="9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" s="13">
-        <v>0.77777777777777779</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -895,34 +895,36 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C19" s="4">
-        <v>588</v>
+        <v>984</v>
       </c>
       <c r="D19" s="9">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E19" s="13">
-        <v>3.3333333333333335</v>
-      </c>
+        <v>3.0714285714285716</v>
+      </c>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>4472</v>
+        <v>5352</v>
       </c>
       <c r="C20" s="6">
-        <v>9693</v>
+        <v>16072</v>
       </c>
       <c r="D20" s="10">
-        <v>393</v>
+        <v>559</v>
       </c>
       <c r="E20" s="14">
-        <v>2.4259259259259256</v>
-      </c>
+        <v>2.2182539682539684</v>
+      </c>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F21" s="1"/>
@@ -1132,20 +1134,32 @@
         <v>101</v>
       </c>
       <c r="I2" s="4">
+        <v>99</v>
+      </c>
+      <c r="J2" s="4">
         <v>100</v>
       </c>
-      <c r="J2" s="4">
-        <v>102</v>
-      </c>
       <c r="K2" s="4">
-        <v>97</v>
-      </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="L2" s="4">
+        <v>120</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>95</v>
+      </c>
+      <c r="P2" s="4">
+        <v>105</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>106</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
@@ -1161,7 +1175,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>903</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1190,20 +1204,32 @@
         <v>103</v>
       </c>
       <c r="I3" s="4">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J3" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K3" s="4">
         <v>107</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="L3" s="4">
+        <v>105</v>
+      </c>
+      <c r="M3" s="4">
+        <v>109</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>106</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>111</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1219,7 +1245,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>860</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1248,20 +1274,32 @@
         <v>110</v>
       </c>
       <c r="I4" s="4">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J4" s="4">
         <v>109</v>
       </c>
       <c r="K4" s="4">
-        <v>129</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>111</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>112</v>
+      </c>
+      <c r="P4" s="4">
+        <v>116</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>128</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -1277,7 +1315,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>905</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1306,20 +1344,32 @@
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J5" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K5" s="4">
-        <v>92</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="L5" s="4">
+        <v>101</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>99</v>
+      </c>
+      <c r="P5" s="4">
+        <v>93</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>98</v>
+      </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -1335,7 +1385,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>756</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1372,12 +1422,24 @@
       <c r="K6" s="4">
         <v>0</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="L6" s="4">
+        <v>117</v>
+      </c>
+      <c r="M6" s="4">
+        <v>111</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>109</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -1393,7 +1455,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>646</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1422,20 +1484,32 @@
         <v>107</v>
       </c>
       <c r="I7" s="4">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J7" s="4">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K7" s="4">
+        <v>107</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
         <v>108</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>109</v>
+      </c>
+      <c r="P7" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>99</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -1451,7 +1525,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>968</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1480,20 +1554,32 @@
         <v>112</v>
       </c>
       <c r="I8" s="4">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8" s="4">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K8" s="4">
-        <v>113</v>
-      </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="L8" s="4">
+        <v>91</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>131</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -1509,7 +1595,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>680</v>
+        <v>987</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1541,17 +1627,29 @@
         <v>0</v>
       </c>
       <c r="J9" s="4">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9" s="4">
-        <v>116</v>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+        <v>115</v>
+      </c>
+      <c r="L9" s="4">
+        <v>110</v>
+      </c>
+      <c r="M9" s="4">
+        <v>106</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>110</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>97</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -1567,7 +1665,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>842</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1596,20 +1694,32 @@
         <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
       </c>
       <c r="K10" s="4">
+        <v>109</v>
+      </c>
+      <c r="L10" s="4">
+        <v>108</v>
+      </c>
+      <c r="M10" s="4">
+        <v>104</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>104</v>
+      </c>
+      <c r="P10" s="4">
+        <v>117</v>
+      </c>
+      <c r="Q10" s="4">
         <v>110</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -1625,7 +1735,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>596</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1654,20 +1764,32 @@
         <v>106</v>
       </c>
       <c r="I11" s="4">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="J11" s="4">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K11" s="4">
-        <v>115</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+        <v>113</v>
+      </c>
+      <c r="L11" s="4">
+        <v>93</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
+        <v>114</v>
+      </c>
+      <c r="P11" s="4">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>110</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -1683,7 +1805,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>786</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1712,20 +1834,32 @@
         <v>98</v>
       </c>
       <c r="I12" s="4">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J12" s="4">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K12" s="4">
-        <v>107</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
+        <v>106</v>
+      </c>
+      <c r="P12" s="4">
+        <v>113</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -1741,7 +1875,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>717</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1770,20 +1904,32 @@
         <v>0</v>
       </c>
       <c r="I13" s="4">
+        <v>99</v>
+      </c>
+      <c r="J13" s="4">
         <v>102</v>
       </c>
-      <c r="J13" s="4">
-        <v>103</v>
-      </c>
       <c r="K13" s="4">
+        <v>93</v>
+      </c>
+      <c r="L13" s="4">
         <v>94</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>68</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>102</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -1799,7 +1945,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>849</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1828,20 +1974,32 @@
         <v>104</v>
       </c>
       <c r="I14" s="4">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J14" s="4">
         <v>107</v>
       </c>
       <c r="K14" s="4">
-        <v>107</v>
-      </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="L14" s="4">
+        <v>104</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>104</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>103</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -1857,7 +2015,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>936</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1894,12 +2052,24 @@
       <c r="K15" s="4">
         <v>0</v>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+      <c r="L15" s="4">
+        <v>102</v>
+      </c>
+      <c r="M15" s="4">
+        <v>106</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>107</v>
+      </c>
+      <c r="P15" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>105</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -1915,7 +2085,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>547</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -1944,20 +2114,32 @@
         <v>98</v>
       </c>
       <c r="I16" s="4">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J16" s="4">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K16" s="4">
-        <v>104</v>
-      </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="L16" s="4">
+        <v>102</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>106</v>
+      </c>
+      <c r="P16" s="4">
+        <v>99</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>106</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -1973,7 +2155,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>848</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2002,20 +2184,32 @@
         <v>126</v>
       </c>
       <c r="I17" s="4">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J17" s="4">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K17" s="4">
         <v>0</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="L17" s="4">
+        <v>108</v>
+      </c>
+      <c r="M17" s="4">
+        <v>110</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>116</v>
+      </c>
+      <c r="P17" s="4">
+        <v>121</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>107</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -2031,7 +2225,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>706</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2060,20 +2254,32 @@
         <v>124</v>
       </c>
       <c r="I18" s="4">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J18" s="4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K18" s="4">
         <v>117</v>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+      <c r="L18" s="4">
+        <v>100</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>114</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>122</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -2089,7 +2295,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>888</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2121,17 +2327,29 @@
         <v>0</v>
       </c>
       <c r="J19" s="4">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K19" s="4">
-        <v>106</v>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="L19" s="4">
+        <v>128</v>
+      </c>
+      <c r="M19" s="4">
+        <v>103</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>107</v>
+      </c>
+      <c r="P19" s="4">
+        <v>99</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>101</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
@@ -2147,7 +2365,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="9">
-        <v>732</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2176,20 +2394,32 @@
         <v>1626</v>
       </c>
       <c r="I20" s="6">
-        <v>1522</v>
+        <v>1492</v>
       </c>
       <c r="J20" s="6">
-        <v>1604</v>
+        <v>1580</v>
       </c>
       <c r="K20" s="6">
-        <v>1622</v>
-      </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
+        <v>1608</v>
+      </c>
+      <c r="L20" s="6">
+        <v>1583</v>
+      </c>
+      <c r="M20" s="6">
+        <v>968</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0</v>
+      </c>
+      <c r="O20" s="6">
+        <v>1461</v>
+      </c>
+      <c r="P20" s="6">
+        <v>1470</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>1845</v>
+      </c>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
       <c r="T20" s="6"/>
@@ -2205,7 +2435,7 @@
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
       <c r="AF20" s="10">
-        <v>14165</v>
+        <v>21424</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2272,7 +2502,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.4259259259259256</v>
+        <v>2.2182539682539684</v>
       </c>
     </row>
   </sheetData>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF10C83A-068B-4BB8-83C5-4166A6CDE4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C51872A-CF79-4475-B4A8-CE0DC99BF882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -572,16 +572,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>499</v>
+        <v>583</v>
       </c>
       <c r="C2" s="4">
-        <v>826</v>
+        <v>975</v>
       </c>
       <c r="D2" s="9">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E2" s="13">
-        <v>2.5</v>
+        <v>2.4705882352941178</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -591,16 +591,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="C3" s="4">
-        <v>1018</v>
+        <v>1208</v>
       </c>
       <c r="D3" s="9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" s="13">
-        <v>2</v>
+        <v>1.8823529411764706</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,16 +610,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="C4" s="4">
-        <v>986</v>
+        <v>1130</v>
       </c>
       <c r="D4" s="9">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E4" s="13">
-        <v>2.3571428571428572</v>
+        <v>2.2352941176470589</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,16 +629,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C5" s="4">
-        <v>830</v>
+        <v>1017</v>
       </c>
       <c r="D5" s="9">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E5" s="13">
-        <v>2.0714285714285716</v>
+        <v>1.9411764705882353</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -648,16 +648,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="C6" s="4">
-        <v>957</v>
+        <v>1112</v>
       </c>
       <c r="D6" s="9">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E6" s="13">
-        <v>2.4285714285714284</v>
+        <v>2.2941176470588234</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,16 +667,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>289</v>
+        <v>370</v>
       </c>
       <c r="C7" s="4">
-        <v>932</v>
+        <v>1202</v>
       </c>
       <c r="D7" s="9">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E7" s="13">
-        <v>2.2142857142857144</v>
+        <v>2.4117647058823528</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -686,16 +686,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="C8" s="4">
-        <v>747</v>
+        <v>934</v>
       </c>
       <c r="D8" s="9">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" s="13">
-        <v>1.5</v>
+        <v>1.4705882352941178</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,16 +705,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>330</v>
+        <v>399</v>
       </c>
       <c r="C9" s="4">
-        <v>1053</v>
+        <v>1205</v>
       </c>
       <c r="D9" s="9">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E9" s="13">
-        <v>2.5714285714285716</v>
+        <v>2.5294117647058822</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,16 +724,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="C10" s="4">
-        <v>705</v>
+        <v>925</v>
       </c>
       <c r="D10" s="9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E10" s="13">
-        <v>2</v>
+        <v>1.7647058823529411</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,16 +743,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="C11" s="4">
-        <v>995</v>
+        <v>1143</v>
       </c>
       <c r="D11" s="9">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E11" s="13">
-        <v>3.3571428571428572</v>
+        <v>3.2941176470588234</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,16 +762,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="C12" s="4">
-        <v>800</v>
+        <v>968</v>
       </c>
       <c r="D12" s="9">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E12" s="13">
-        <v>2.7857142857142856</v>
+        <v>2.6470588235294117</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -781,16 +781,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="C13" s="4">
-        <v>888</v>
+        <v>1057</v>
       </c>
       <c r="D13" s="9">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E13" s="13">
-        <v>2.8571428571428572</v>
+        <v>3</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,16 +800,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="C14" s="4">
-        <v>685</v>
+        <v>915</v>
       </c>
       <c r="D14" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E14" s="13">
-        <v>1.7142857142857142</v>
+        <v>1.5294117647058822</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,16 +819,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="C15" s="4">
-        <v>890</v>
+        <v>1181</v>
       </c>
       <c r="D15" s="9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E15" s="13">
-        <v>1.7142857142857142</v>
+        <v>1.7058823529411764</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -838,16 +838,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="C16" s="4">
-        <v>899</v>
+        <v>1066</v>
       </c>
       <c r="D16" s="9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" s="13">
-        <v>2.7142857142857144</v>
+        <v>2.4705882352941178</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -857,16 +857,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>313</v>
+        <v>401</v>
       </c>
       <c r="C17" s="4">
-        <v>932</v>
+        <v>1171</v>
       </c>
       <c r="D17" s="9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E17" s="13">
-        <v>1.2857142857142858</v>
+        <v>1.3529411764705883</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -876,16 +876,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C18" s="4">
-        <v>945</v>
+        <v>1174</v>
       </c>
       <c r="D18" s="9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E18" s="13">
-        <v>0.7857142857142857</v>
+        <v>0.76470588235294112</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -895,16 +895,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="C19" s="4">
-        <v>984</v>
+        <v>1185</v>
       </c>
       <c r="D19" s="9">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E19" s="13">
-        <v>3.0714285714285716</v>
+        <v>3</v>
       </c>
       <c r="H19" s="1"/>
     </row>
@@ -913,16 +913,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>5352</v>
+        <v>6346</v>
       </c>
       <c r="C20" s="6">
-        <v>16072</v>
+        <v>19568</v>
       </c>
       <c r="D20" s="10">
-        <v>559</v>
+        <v>659</v>
       </c>
       <c r="E20" s="14">
-        <v>2.2182539682539684</v>
+        <v>2.15359477124183</v>
       </c>
       <c r="H20" s="1"/>
     </row>
@@ -1160,9 +1160,15 @@
       <c r="Q2" s="4">
         <v>106</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>111</v>
+      </c>
+      <c r="T2" s="4">
+        <v>122</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1175,7 +1181,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1325</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1230,9 +1236,15 @@
       <c r="Q3" s="4">
         <v>111</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="R3" s="4">
+        <v>114</v>
+      </c>
+      <c r="S3" s="4">
+        <v>114</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -1245,7 +1257,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1288</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1300,9 +1312,15 @@
       <c r="Q4" s="4">
         <v>128</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>87</v>
+      </c>
+      <c r="T4" s="4">
+        <v>107</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1315,7 +1333,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1370</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1370,9 +1388,15 @@
       <c r="Q5" s="4">
         <v>98</v>
       </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="R5" s="4">
+        <v>97</v>
+      </c>
+      <c r="S5" s="4">
+        <v>113</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -1385,7 +1409,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>1144</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1440,9 +1464,15 @@
       <c r="Q6" s="4">
         <v>109</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="R6" s="4">
+        <v>118</v>
+      </c>
+      <c r="S6" s="4">
+        <v>118</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1455,7 +1485,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>983</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1510,9 +1540,15 @@
       <c r="Q7" s="4">
         <v>99</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="R7" s="4">
+        <v>109</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>112</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1525,7 +1561,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1383</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1580,9 +1616,15 @@
       <c r="Q8" s="4">
         <v>131</v>
       </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="R8" s="4">
+        <v>106</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>159</v>
+      </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1595,7 +1637,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>987</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1650,9 +1692,15 @@
       <c r="Q9" s="4">
         <v>97</v>
       </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="R9" s="4">
+        <v>111</v>
+      </c>
+      <c r="S9" s="4">
+        <v>94</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -1665,7 +1713,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1263</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1720,9 +1768,15 @@
       <c r="Q10" s="4">
         <v>110</v>
       </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
+      <c r="R10" s="4">
+        <v>120</v>
+      </c>
+      <c r="S10" s="4">
+        <v>106</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
@@ -1735,7 +1789,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1137</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1790,9 +1844,15 @@
       <c r="Q11" s="4">
         <v>110</v>
       </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4">
+        <v>109</v>
+      </c>
+      <c r="T11" s="4">
+        <v>108</v>
+      </c>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
@@ -1805,7 +1865,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1185</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1860,9 +1920,15 @@
       <c r="Q12" s="4">
         <v>0</v>
       </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="R12" s="4">
+        <v>126</v>
+      </c>
+      <c r="S12" s="4">
+        <v>59</v>
+      </c>
+      <c r="T12" s="4">
+        <v>113</v>
+      </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
@@ -1875,7 +1941,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>932</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1930,9 +1996,15 @@
       <c r="Q13" s="4">
         <v>102</v>
       </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
+      <c r="R13" s="4">
+        <v>125</v>
+      </c>
+      <c r="S13" s="4">
+        <v>101</v>
+      </c>
+      <c r="T13" s="4">
+        <v>115</v>
+      </c>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
@@ -1945,7 +2017,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1108</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2000,9 +2072,15 @@
       <c r="Q14" s="4">
         <v>103</v>
       </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="R14" s="4">
+        <v>112</v>
+      </c>
+      <c r="S14" s="4">
+        <v>100</v>
+      </c>
+      <c r="T14" s="4">
+        <v>115</v>
+      </c>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -2015,7 +2093,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1245</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2070,9 +2148,15 @@
       <c r="Q15" s="4">
         <v>105</v>
       </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
+      <c r="R15" s="4">
+        <v>138</v>
+      </c>
+      <c r="S15" s="4">
+        <v>114</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -2085,7 +2169,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1070</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2140,9 +2224,15 @@
       <c r="Q16" s="4">
         <v>106</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
+      <c r="R16" s="4">
+        <v>129</v>
+      </c>
+      <c r="S16" s="4">
+        <v>113</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -2155,7 +2245,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1254</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2210,9 +2300,15 @@
       <c r="Q17" s="4">
         <v>107</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
+      <c r="R17" s="4">
+        <v>106</v>
+      </c>
+      <c r="S17" s="4">
+        <v>121</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0</v>
+      </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -2225,7 +2321,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1262</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2280,9 +2376,15 @@
       <c r="Q18" s="4">
         <v>122</v>
       </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
+      <c r="R18" s="4">
+        <v>122</v>
+      </c>
+      <c r="S18" s="4">
+        <v>118</v>
+      </c>
+      <c r="T18" s="4">
+        <v>111</v>
+      </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -2295,7 +2397,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1221</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2350,9 +2452,15 @@
       <c r="Q19" s="4">
         <v>101</v>
       </c>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
+      <c r="R19" s="4">
+        <v>105</v>
+      </c>
+      <c r="S19" s="4">
+        <v>112</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -2365,7 +2473,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="9">
-        <v>1267</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2420,9 +2528,15 @@
       <c r="Q20" s="6">
         <v>1845</v>
       </c>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
+      <c r="R20" s="6">
+        <v>1738</v>
+      </c>
+      <c r="S20" s="6">
+        <v>1690</v>
+      </c>
+      <c r="T20" s="6">
+        <v>1062</v>
+      </c>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
@@ -2435,7 +2549,7 @@
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
       <c r="AF20" s="10">
-        <v>21424</v>
+        <v>25914</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2502,7 +2616,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.2182539682539684</v>
+        <v>2.15359477124183</v>
       </c>
     </row>
   </sheetData>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C51872A-CF79-4475-B4A8-CE0DC99BF882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD7753-1A57-433B-A1FE-5F5A3679D7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,10 +578,10 @@
         <v>975</v>
       </c>
       <c r="D2" s="9">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E2" s="13">
-        <v>2.4705882352941178</v>
+        <v>2.8823529411764706</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -597,10 +597,10 @@
         <v>1208</v>
       </c>
       <c r="D3" s="9">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E3" s="13">
-        <v>1.8823529411764706</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -616,10 +616,10 @@
         <v>1130</v>
       </c>
       <c r="D4" s="9">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4" s="13">
-        <v>2.2352941176470589</v>
+        <v>2.9411764705882355</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -635,10 +635,10 @@
         <v>1017</v>
       </c>
       <c r="D5" s="9">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E5" s="13">
-        <v>1.9411764705882353</v>
+        <v>2.2941176470588234</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -654,10 +654,10 @@
         <v>1112</v>
       </c>
       <c r="D6" s="9">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E6" s="13">
-        <v>2.2941176470588234</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -673,10 +673,10 @@
         <v>1202</v>
       </c>
       <c r="D7" s="9">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E7" s="13">
-        <v>2.4117647058823528</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -692,10 +692,10 @@
         <v>934</v>
       </c>
       <c r="D8" s="9">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E8" s="13">
-        <v>1.4705882352941178</v>
+        <v>2.2352941176470589</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -711,10 +711,10 @@
         <v>1205</v>
       </c>
       <c r="D9" s="9">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E9" s="13">
-        <v>2.5294117647058822</v>
+        <v>3.8235294117647061</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -730,10 +730,10 @@
         <v>925</v>
       </c>
       <c r="D10" s="9">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E10" s="13">
-        <v>1.7647058823529411</v>
+        <v>2.1764705882352939</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -749,10 +749,10 @@
         <v>1143</v>
       </c>
       <c r="D11" s="9">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E11" s="13">
-        <v>3.2941176470588234</v>
+        <v>4.0588235294117645</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -768,10 +768,10 @@
         <v>968</v>
       </c>
       <c r="D12" s="9">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E12" s="13">
-        <v>2.6470588235294117</v>
+        <v>3.4705882352941178</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -787,10 +787,10 @@
         <v>1057</v>
       </c>
       <c r="D13" s="9">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E13" s="13">
-        <v>3</v>
+        <v>3.3529411764705883</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -806,10 +806,10 @@
         <v>915</v>
       </c>
       <c r="D14" s="9">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E14" s="13">
-        <v>1.5294117647058822</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -825,10 +825,10 @@
         <v>1181</v>
       </c>
       <c r="D15" s="9">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E15" s="13">
-        <v>1.7058823529411764</v>
+        <v>2.2352941176470589</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -844,10 +844,10 @@
         <v>1066</v>
       </c>
       <c r="D16" s="9">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E16" s="13">
-        <v>2.4705882352941178</v>
+        <v>3.2941176470588234</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -863,10 +863,10 @@
         <v>1171</v>
       </c>
       <c r="D17" s="9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E17" s="13">
-        <v>1.3529411764705883</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -882,10 +882,10 @@
         <v>1174</v>
       </c>
       <c r="D18" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="13">
-        <v>0.76470588235294112</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -901,10 +901,10 @@
         <v>1185</v>
       </c>
       <c r="D19" s="9">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E19" s="13">
-        <v>3</v>
+        <v>3.5882352941176472</v>
       </c>
       <c r="H19" s="1"/>
     </row>
@@ -919,10 +919,10 @@
         <v>19568</v>
       </c>
       <c r="D20" s="10">
-        <v>659</v>
+        <v>842</v>
       </c>
       <c r="E20" s="14">
-        <v>2.15359477124183</v>
+        <v>2.7516339869281046</v>
       </c>
       <c r="H20" s="1"/>
     </row>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.15359477124183</v>
+        <v>2.7516339869281046</v>
       </c>
     </row>
   </sheetData>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD7753-1A57-433B-A1FE-5F5A3679D7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966D2B91-6D3D-44E1-975B-F436D630B7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -572,16 +572,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="C2" s="4">
-        <v>975</v>
+        <v>1046</v>
       </c>
       <c r="D2" s="9">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E2" s="13">
-        <v>2.8823529411764706</v>
+        <v>2.736842105263158</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -591,16 +591,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C3" s="4">
-        <v>1208</v>
+        <v>1291</v>
       </c>
       <c r="D3" s="9">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13">
-        <v>2.3529411764705883</v>
+        <v>2.4210526315789473</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,16 +610,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>434</v>
+        <v>488</v>
       </c>
       <c r="C4" s="4">
-        <v>1130</v>
+        <v>1290</v>
       </c>
       <c r="D4" s="9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E4" s="13">
-        <v>2.9411764705882355</v>
+        <v>2.8947368421052633</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,16 +629,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>337</v>
+        <v>380</v>
       </c>
       <c r="C5" s="4">
-        <v>1017</v>
+        <v>1161</v>
       </c>
       <c r="D5" s="9">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E5" s="13">
-        <v>2.2941176470588234</v>
+        <v>2.4210526315789473</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -648,16 +648,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="C6" s="4">
-        <v>1112</v>
+        <v>1274</v>
       </c>
       <c r="D6" s="9">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E6" s="13">
-        <v>3</v>
+        <v>2.9473684210526314</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,13 +667,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="C7" s="4">
-        <v>1202</v>
+        <v>1404</v>
       </c>
       <c r="D7" s="9">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E7" s="13">
         <v>3</v>
@@ -686,16 +686,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="C8" s="4">
-        <v>934</v>
+        <v>1103</v>
       </c>
       <c r="D8" s="9">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E8" s="13">
-        <v>2.2352941176470589</v>
+        <v>2.1578947368421053</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,16 +705,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C9" s="4">
-        <v>1205</v>
+        <v>1361</v>
       </c>
       <c r="D9" s="9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E9" s="13">
-        <v>3.8235294117647061</v>
+        <v>3.6842105263157894</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,16 +724,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>327</v>
+        <v>392</v>
       </c>
       <c r="C10" s="4">
-        <v>925</v>
+        <v>1083</v>
       </c>
       <c r="D10" s="9">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" s="13">
-        <v>2.1764705882352939</v>
+        <v>2.3157894736842106</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,16 +743,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="C11" s="4">
-        <v>1143</v>
+        <v>1323</v>
       </c>
       <c r="D11" s="9">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E11" s="13">
-        <v>4.0588235294117645</v>
+        <v>3.9473684210526314</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,16 +762,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>395</v>
+        <v>461</v>
       </c>
       <c r="C12" s="4">
-        <v>968</v>
+        <v>1113</v>
       </c>
       <c r="D12" s="9">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E12" s="13">
-        <v>3.4705882352941178</v>
+        <v>3.4736842105263159</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -781,16 +781,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>345</v>
+        <v>384</v>
       </c>
       <c r="C13" s="4">
-        <v>1057</v>
+        <v>1208</v>
       </c>
       <c r="D13" s="9">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E13" s="13">
-        <v>3.3529411764705883</v>
+        <v>3.4210526315789473</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,16 +800,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="C14" s="4">
-        <v>915</v>
+        <v>1070</v>
       </c>
       <c r="D14" s="9">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E14" s="13">
-        <v>2</v>
+        <v>2.3157894736842106</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,16 +819,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="C15" s="4">
-        <v>1181</v>
+        <v>1352</v>
       </c>
       <c r="D15" s="9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" s="13">
-        <v>2.2352941176470589</v>
+        <v>2.1052631578947367</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -838,16 +838,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="C16" s="4">
-        <v>1066</v>
+        <v>1232</v>
       </c>
       <c r="D16" s="9">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E16" s="13">
-        <v>3.2941176470588234</v>
+        <v>3.3157894736842106</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -857,13 +857,13 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="C17" s="4">
-        <v>1171</v>
+        <v>1331</v>
       </c>
       <c r="D17" s="9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E17" s="13">
         <v>2</v>
@@ -876,16 +876,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C18" s="4">
-        <v>1174</v>
+        <v>1372</v>
       </c>
       <c r="D18" s="9">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" s="13">
-        <v>0.82352941176470584</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -895,16 +895,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C19" s="4">
-        <v>1185</v>
+        <v>1273</v>
       </c>
       <c r="D19" s="9">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E19" s="13">
-        <v>3.5882352941176472</v>
+        <v>3.5263157894736841</v>
       </c>
       <c r="H19" s="1"/>
     </row>
@@ -913,16 +913,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>6346</v>
+        <v>7142</v>
       </c>
       <c r="C20" s="6">
-        <v>19568</v>
+        <v>22287</v>
       </c>
       <c r="D20" s="10">
-        <v>842</v>
+        <v>941</v>
       </c>
       <c r="E20" s="14">
-        <v>2.7516339869281046</v>
+        <v>2.7514619883040936</v>
       </c>
       <c r="H20" s="1"/>
     </row>
@@ -1169,9 +1169,15 @@
       <c r="T2" s="4">
         <v>122</v>
       </c>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>96</v>
+      </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
@@ -1181,7 +1187,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1558</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1245,9 +1251,15 @@
       <c r="T3" s="4">
         <v>0</v>
       </c>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>104</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
@@ -1257,7 +1269,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1516</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1321,9 +1333,15 @@
       <c r="T4" s="4">
         <v>107</v>
       </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <v>103</v>
+      </c>
+      <c r="W4" s="4">
+        <v>111</v>
+      </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
@@ -1333,7 +1351,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1564</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1397,9 +1415,15 @@
       <c r="T5" s="4">
         <v>0</v>
       </c>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <v>95</v>
+      </c>
+      <c r="W5" s="4">
+        <v>92</v>
+      </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
@@ -1409,7 +1433,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>1354</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1473,9 +1497,15 @@
       <c r="T6" s="4">
         <v>0</v>
       </c>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>109</v>
+      </c>
+      <c r="W6" s="4">
+        <v>109</v>
+      </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
@@ -1485,7 +1515,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1219</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1549,9 +1579,15 @@
       <c r="T7" s="4">
         <v>112</v>
       </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>96</v>
+      </c>
+      <c r="W7" s="4">
+        <v>106</v>
+      </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
@@ -1561,7 +1597,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1604</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1625,9 +1661,15 @@
       <c r="T8" s="4">
         <v>159</v>
       </c>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>98</v>
+      </c>
+      <c r="W8" s="4">
+        <v>125</v>
+      </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
@@ -1637,7 +1679,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1252</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1701,9 +1743,15 @@
       <c r="T9" s="4">
         <v>0</v>
       </c>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <v>106</v>
+      </c>
+      <c r="W9" s="4">
+        <v>112</v>
+      </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
@@ -1713,7 +1761,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1468</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1777,9 +1825,15 @@
       <c r="T10" s="4">
         <v>0</v>
       </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>108</v>
+      </c>
+      <c r="W10" s="4">
+        <v>103</v>
+      </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
@@ -1789,7 +1843,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1363</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1853,9 +1907,15 @@
       <c r="T11" s="4">
         <v>108</v>
       </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
+      <c r="U11" s="4">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4">
+        <v>94</v>
+      </c>
+      <c r="W11" s="4">
+        <v>96</v>
+      </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
@@ -1865,7 +1925,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1402</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1929,9 +1989,15 @@
       <c r="T12" s="4">
         <v>113</v>
       </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
+      <c r="U12" s="4">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
+        <v>107</v>
+      </c>
+      <c r="W12" s="4">
+        <v>96</v>
+      </c>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
@@ -1941,7 +2007,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1230</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2005,9 +2071,15 @@
       <c r="T13" s="4">
         <v>115</v>
       </c>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <v>105</v>
+      </c>
+      <c r="W13" s="4">
+        <v>103</v>
+      </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
@@ -2017,7 +2089,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1449</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2081,9 +2153,15 @@
       <c r="T14" s="4">
         <v>115</v>
       </c>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
+        <v>109</v>
+      </c>
+      <c r="W14" s="4">
+        <v>111</v>
+      </c>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
@@ -2093,7 +2171,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1572</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2157,9 +2235,15 @@
       <c r="T15" s="4">
         <v>0</v>
       </c>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>111</v>
+      </c>
+      <c r="W15" s="4">
+        <v>111</v>
+      </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
@@ -2169,7 +2253,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1322</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2233,9 +2317,15 @@
       <c r="T16" s="4">
         <v>0</v>
       </c>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>105</v>
+      </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
@@ -2245,7 +2335,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1496</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2309,9 +2399,15 @@
       <c r="T17" s="4">
         <v>0</v>
       </c>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
+        <v>114</v>
+      </c>
+      <c r="W17" s="4">
+        <v>111</v>
+      </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
@@ -2321,7 +2417,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1489</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2385,9 +2481,15 @@
       <c r="T18" s="4">
         <v>111</v>
       </c>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <v>127</v>
+      </c>
+      <c r="W18" s="4">
+        <v>127</v>
+      </c>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
@@ -2397,7 +2499,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1572</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2461,9 +2563,15 @@
       <c r="T19" s="4">
         <v>0</v>
       </c>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>106</v>
+      </c>
+      <c r="W19" s="4">
+        <v>109</v>
+      </c>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
@@ -2473,7 +2581,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="9">
-        <v>1484</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2537,9 +2645,15 @@
       <c r="T20" s="6">
         <v>1062</v>
       </c>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
+      <c r="U20" s="6">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6">
+        <v>1692</v>
+      </c>
+      <c r="W20" s="6">
+        <v>1823</v>
+      </c>
       <c r="X20" s="6"/>
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
@@ -2549,7 +2663,7 @@
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
       <c r="AF20" s="10">
-        <v>25914</v>
+        <v>29429</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2616,7 +2730,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.7516339869281046</v>
+        <v>2.7514619883040936</v>
       </c>
     </row>
   </sheetData>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966D2B91-6D3D-44E1-975B-F436D630B7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC2F6F4-CB2E-4E85-816F-B446741F7A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -204,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -226,6 +226,7 @@
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -540,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
@@ -572,16 +573,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>608</v>
+        <v>657</v>
       </c>
       <c r="C2" s="4">
-        <v>1046</v>
+        <v>1208</v>
       </c>
       <c r="D2" s="9">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="E2" s="13">
-        <v>2.736842105263158</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -591,16 +592,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="C3" s="4">
-        <v>1291</v>
+        <v>1472</v>
       </c>
       <c r="D3" s="9">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="E3" s="13">
-        <v>2.4210526315789473</v>
+        <v>3.1904761904761907</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,16 +611,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>488</v>
+        <v>551</v>
       </c>
       <c r="C4" s="4">
-        <v>1290</v>
+        <v>1439</v>
       </c>
       <c r="D4" s="9">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="E4" s="13">
-        <v>2.8947368421052633</v>
+        <v>4.4761904761904763</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,16 +630,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C5" s="4">
-        <v>1161</v>
+        <v>1170</v>
       </c>
       <c r="D5" s="9">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E5" s="13">
-        <v>2.4210526315789473</v>
+        <v>2.7142857142857144</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -648,16 +649,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="C6" s="4">
-        <v>1274</v>
+        <v>1355</v>
       </c>
       <c r="D6" s="9">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E6" s="13">
-        <v>2.9473684210526314</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,16 +668,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>422</v>
+        <v>480</v>
       </c>
       <c r="C7" s="4">
-        <v>1404</v>
+        <v>1595</v>
       </c>
       <c r="D7" s="9">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E7" s="13">
-        <v>3</v>
+        <v>4.0952380952380949</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -686,16 +687,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="C8" s="4">
-        <v>1103</v>
+        <v>1283</v>
       </c>
       <c r="D8" s="9">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="E8" s="13">
-        <v>2.1578947368421053</v>
+        <v>3.0952380952380953</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,16 +706,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="C9" s="4">
-        <v>1361</v>
+        <v>1535</v>
       </c>
       <c r="D9" s="9">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E9" s="13">
-        <v>3.6842105263157894</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,16 +725,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>392</v>
+        <v>444</v>
       </c>
       <c r="C10" s="4">
-        <v>1083</v>
+        <v>1264</v>
       </c>
       <c r="D10" s="9">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E10" s="13">
-        <v>2.3157894736842106</v>
+        <v>3.2380952380952381</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,16 +744,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>363</v>
+        <v>412</v>
       </c>
       <c r="C11" s="4">
-        <v>1323</v>
+        <v>1499</v>
       </c>
       <c r="D11" s="9">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E11" s="13">
-        <v>3.9473684210526314</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,16 +763,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="C12" s="4">
-        <v>1113</v>
+        <v>1190</v>
       </c>
       <c r="D12" s="9">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E12" s="13">
-        <v>3.4736842105263159</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -781,16 +782,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="C13" s="4">
-        <v>1208</v>
+        <v>1379</v>
       </c>
       <c r="D13" s="9">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E13" s="13">
-        <v>3.4210526315789473</v>
+        <v>3.6190476190476191</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,16 +801,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="C14" s="4">
-        <v>1070</v>
+        <v>1249</v>
       </c>
       <c r="D14" s="9">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E14" s="13">
-        <v>2.3157894736842106</v>
+        <v>2.9523809523809526</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,16 +820,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="C15" s="4">
-        <v>1352</v>
+        <v>1528</v>
       </c>
       <c r="D15" s="9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E15" s="13">
-        <v>2.1052631578947367</v>
+        <v>2.3809523809523809</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -838,128 +839,129 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="C16" s="4">
-        <v>1232</v>
+        <v>1399</v>
       </c>
       <c r="D16" s="9">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E16" s="13">
-        <v>3.3157894736842106</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>461</v>
+        <v>519</v>
       </c>
       <c r="C17" s="4">
-        <v>1331</v>
+        <v>1486</v>
       </c>
       <c r="D17" s="9">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E17" s="13">
-        <v>2</v>
+        <v>2.3809523809523809</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C18" s="4">
-        <v>1372</v>
+        <v>1461</v>
       </c>
       <c r="D18" s="9">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E18" s="13">
-        <v>0.84210526315789469</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="C19" s="4">
-        <v>1273</v>
+        <v>1454</v>
       </c>
       <c r="D19" s="9">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E19" s="13">
-        <v>3.5263157894736841</v>
+        <v>4.3809523809523814</v>
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>7142</v>
+        <v>7913</v>
       </c>
       <c r="C20" s="6">
-        <v>22287</v>
+        <v>24966</v>
       </c>
       <c r="D20" s="10">
-        <v>941</v>
+        <v>1318</v>
       </c>
       <c r="E20" s="14">
-        <v>2.7514619883040936</v>
+        <v>3.4867724867724865</v>
       </c>
       <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
@@ -982,7 +984,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G20">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1178,8 +1192,12 @@
       <c r="W2" s="4">
         <v>96</v>
       </c>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="X2" s="4">
+        <v>104</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>107</v>
+      </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
@@ -1187,7 +1205,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1654</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1260,8 +1278,12 @@
       <c r="W3" s="4">
         <v>0</v>
       </c>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="X3" s="4">
+        <v>112</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>112</v>
+      </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
@@ -1269,7 +1291,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1620</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1342,8 +1364,12 @@
       <c r="W4" s="4">
         <v>111</v>
       </c>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="X4" s="4">
+        <v>103</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>109</v>
+      </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
@@ -1351,7 +1377,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1778</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1424,8 +1450,12 @@
       <c r="W5" s="4">
         <v>92</v>
       </c>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
+      <c r="X5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>21</v>
+      </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
@@ -1433,7 +1463,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>1541</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1506,8 +1536,12 @@
       <c r="W6" s="4">
         <v>109</v>
       </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
+      <c r="X6" s="4">
+        <v>116</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>117</v>
+      </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
@@ -1515,7 +1549,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1437</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1588,8 +1622,12 @@
       <c r="W7" s="4">
         <v>106</v>
       </c>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
+      <c r="X7" s="4">
+        <v>111</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>106</v>
+      </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
@@ -1597,7 +1635,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>1806</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1670,8 +1708,12 @@
       <c r="W8" s="4">
         <v>125</v>
       </c>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
+      <c r="X8" s="4">
+        <v>122</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>111</v>
+      </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
@@ -1679,7 +1721,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1475</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1752,8 +1794,12 @@
       <c r="W9" s="4">
         <v>112</v>
       </c>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
+      <c r="X9" s="4">
+        <v>108</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>117</v>
+      </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
@@ -1761,7 +1807,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1686</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1834,8 +1880,12 @@
       <c r="W10" s="4">
         <v>103</v>
       </c>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
+      <c r="X10" s="4">
+        <v>106</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>0</v>
+      </c>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
@@ -1843,7 +1893,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1574</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1916,8 +1966,12 @@
       <c r="W11" s="4">
         <v>96</v>
       </c>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
+      <c r="X11" s="4">
+        <v>108</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>100</v>
+      </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
@@ -1925,7 +1979,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1592</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1998,8 +2052,12 @@
       <c r="W12" s="4">
         <v>96</v>
       </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
+      <c r="X12" s="4">
+        <v>122</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>111</v>
+      </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
@@ -2007,7 +2065,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1433</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2080,8 +2138,12 @@
       <c r="W13" s="4">
         <v>103</v>
       </c>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
+      <c r="X13" s="4">
+        <v>110</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>101</v>
+      </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
       <c r="AB13" s="4"/>
@@ -2089,7 +2151,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1657</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2162,8 +2224,12 @@
       <c r="W14" s="4">
         <v>111</v>
       </c>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
+      <c r="X14" s="4">
+        <v>111</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>102</v>
+      </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
@@ -2171,7 +2237,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>1792</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2244,8 +2310,12 @@
       <c r="W15" s="4">
         <v>111</v>
       </c>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
+      <c r="X15" s="4">
+        <v>101</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>0</v>
+      </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
@@ -2253,7 +2323,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1544</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2326,8 +2396,12 @@
       <c r="W16" s="4">
         <v>105</v>
       </c>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
+      <c r="X16" s="4">
+        <v>112</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>106</v>
+      </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
@@ -2335,7 +2409,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1601</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2408,8 +2482,12 @@
       <c r="W17" s="4">
         <v>111</v>
       </c>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
+      <c r="X17" s="4">
+        <v>106</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>114</v>
+      </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
       <c r="AB17" s="4"/>
@@ -2417,7 +2495,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1714</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2490,8 +2568,12 @@
       <c r="W18" s="4">
         <v>127</v>
       </c>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
+      <c r="X18" s="4">
+        <v>124</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>125</v>
+      </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
@@ -2499,7 +2581,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>1826</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2572,8 +2654,12 @@
       <c r="W19" s="4">
         <v>109</v>
       </c>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
+      <c r="X19" s="4">
+        <v>115</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>0</v>
+      </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
@@ -2581,7 +2667,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="9">
-        <v>1699</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2654,8 +2740,12 @@
       <c r="W20" s="6">
         <v>1823</v>
       </c>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
+      <c r="X20" s="6">
+        <v>1891</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>1559</v>
+      </c>
       <c r="Z20" s="6"/>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
@@ -2663,7 +2753,7 @@
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
       <c r="AF20" s="10">
-        <v>29429</v>
+        <v>32879</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2717,21 +2807,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.7514619883040936</v>
-      </c>
+        <v>3.4867724867724865</v>
+      </c>
+      <c r="D2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC2F6F4-CB2E-4E85-816F-B446741F7A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D740AF2-B6E3-4B1A-B3F4-E52D036A760F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -227,6 +227,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -541,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
@@ -573,57 +574,60 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="C2" s="4">
-        <v>1208</v>
+        <v>1279</v>
       </c>
       <c r="D2" s="9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E2" s="13">
-        <v>3.8095238095238093</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>372</v>
+        <v>422</v>
       </c>
       <c r="C3" s="4">
-        <v>1472</v>
+        <v>1645</v>
       </c>
       <c r="D3" s="9">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E3" s="13">
-        <v>3.1904761904761907</v>
+        <v>3.3809523809523809</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C4" s="4">
-        <v>1439</v>
+        <v>1511</v>
       </c>
       <c r="D4" s="9">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E4" s="13">
-        <v>4.4761904761904763</v>
+        <v>4.7619047619047619</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -636,332 +640,348 @@
         <v>1170</v>
       </c>
       <c r="D5" s="9">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E5" s="13">
-        <v>2.7142857142857144</v>
+        <v>2.8571428571428572</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>459</v>
+        <v>554</v>
       </c>
       <c r="C6" s="4">
-        <v>1355</v>
+        <v>1519</v>
       </c>
       <c r="D6" s="9">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" s="13">
-        <v>4.1428571428571432</v>
+        <v>4.2380952380952381</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>480</v>
+        <v>509</v>
       </c>
       <c r="C7" s="4">
-        <v>1595</v>
+        <v>1684</v>
       </c>
       <c r="D7" s="9">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E7" s="13">
-        <v>4.0952380952380949</v>
+        <v>4.3809523809523814</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>387</v>
+        <v>455</v>
       </c>
       <c r="C8" s="4">
-        <v>1283</v>
+        <v>1435</v>
       </c>
       <c r="D8" s="9">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E8" s="13">
-        <v>3.0952380952380953</v>
+        <v>3.5238095238095237</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="C9" s="4">
-        <v>1535</v>
+        <v>1622</v>
       </c>
       <c r="D9" s="9">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E9" s="13">
-        <v>4.333333333333333</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="C10" s="4">
-        <v>1264</v>
+        <v>1337</v>
       </c>
       <c r="D10" s="9">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E10" s="13">
-        <v>3.2380952380952381</v>
+        <v>3.5238095238095237</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="C11" s="4">
-        <v>1499</v>
+        <v>1576</v>
       </c>
       <c r="D11" s="9">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E11" s="13">
-        <v>4.333333333333333</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>490</v>
+        <v>577</v>
       </c>
       <c r="C12" s="4">
-        <v>1190</v>
+        <v>1324</v>
       </c>
       <c r="D12" s="9">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E12" s="13">
-        <v>4.1428571428571432</v>
+        <v>4.7619047619047619</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C13" s="4">
-        <v>1379</v>
+        <v>1462</v>
       </c>
       <c r="D13" s="9">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E13" s="13">
-        <v>3.6190476190476191</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C14" s="4">
-        <v>1249</v>
+        <v>1336</v>
       </c>
       <c r="D14" s="9">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E14" s="13">
-        <v>2.9523809523809526</v>
+        <v>3.3809523809523809</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="C15" s="4">
-        <v>1528</v>
+        <v>1617</v>
       </c>
       <c r="D15" s="9">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E15" s="13">
-        <v>2.3809523809523809</v>
+        <v>2.5238095238095237</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="C16" s="4">
-        <v>1399</v>
+        <v>1470</v>
       </c>
       <c r="D16" s="9">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E16" s="13">
-        <v>3.8095238095238093</v>
+        <v>4.0952380952380949</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G16" s="1"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C17" s="4">
-        <v>1486</v>
+        <v>1565</v>
       </c>
       <c r="D17" s="9">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E17" s="13">
-        <v>2.3809523809523809</v>
+        <v>2.5238095238095237</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G17" s="1"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="C18" s="4">
-        <v>1461</v>
+        <v>1644</v>
       </c>
       <c r="D18" s="9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E18" s="13">
-        <v>1.6666666666666667</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G18" s="1"/>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C19" s="4">
-        <v>1454</v>
+        <v>1543</v>
       </c>
       <c r="D19" s="9">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E19" s="13">
-        <v>4.3809523809523814</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>7913</v>
+        <v>8578</v>
       </c>
       <c r="C20" s="6">
-        <v>24966</v>
+        <v>26739</v>
       </c>
       <c r="D20" s="10">
-        <v>1318</v>
+        <v>1432</v>
       </c>
       <c r="E20" s="14">
-        <v>3.4867724867724865</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3.7883597883597884</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
@@ -984,19 +1004,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E19">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1198,14 +1206,18 @@
       <c r="Y2" s="4">
         <v>107</v>
       </c>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="Z2" s="4">
+        <v>102</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>1865</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1284,14 +1296,18 @@
       <c r="Y3" s="4">
         <v>112</v>
       </c>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="Z3" s="4">
+        <v>113</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>110</v>
+      </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>1844</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1370,14 +1386,18 @@
       <c r="Y4" s="4">
         <v>109</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="Z4" s="4">
+        <v>97</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>1990</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1456,8 +1476,12 @@
       <c r="Y5" s="4">
         <v>21</v>
       </c>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="Z5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>0</v>
+      </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
@@ -1542,14 +1566,18 @@
       <c r="Y6" s="4">
         <v>117</v>
       </c>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="Z6" s="4">
+        <v>112</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>108</v>
+      </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="9">
-        <v>1670</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1628,14 +1656,18 @@
       <c r="Y7" s="4">
         <v>106</v>
       </c>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="Z7" s="4">
+        <v>112</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>0</v>
+      </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>2023</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1714,14 +1746,18 @@
       <c r="Y8" s="4">
         <v>111</v>
       </c>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="Z8" s="4">
+        <v>105</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>0</v>
+      </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>1708</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1800,14 +1836,18 @@
       <c r="Y9" s="4">
         <v>117</v>
       </c>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="Z9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>114</v>
+      </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>1911</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1886,14 +1926,18 @@
       <c r="Y10" s="4">
         <v>0</v>
       </c>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="Z10" s="4">
+        <v>114</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>107</v>
+      </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>1680</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1972,14 +2016,18 @@
       <c r="Y11" s="4">
         <v>100</v>
       </c>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="Z11" s="4">
+        <v>106</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>0</v>
+      </c>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>1800</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2058,14 +2106,18 @@
       <c r="Y12" s="4">
         <v>111</v>
       </c>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="Z12" s="4">
+        <v>105</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>3</v>
+      </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>1666</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2144,14 +2196,18 @@
       <c r="Y13" s="4">
         <v>101</v>
       </c>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="Z13" s="4">
+        <v>102</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>1868</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2230,14 +2286,18 @@
       <c r="Y14" s="4">
         <v>102</v>
       </c>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="Z14" s="4">
+        <v>104</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>0</v>
+      </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>2005</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2316,14 +2376,18 @@
       <c r="Y15" s="4">
         <v>0</v>
       </c>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="Z15" s="4">
+        <v>111</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>110</v>
+      </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>1645</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2402,14 +2466,18 @@
       <c r="Y16" s="4">
         <v>106</v>
       </c>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>115</v>
+      </c>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>1819</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2488,14 +2556,18 @@
       <c r="Y17" s="4">
         <v>114</v>
       </c>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="Z17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>111</v>
+      </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>1934</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2574,14 +2646,18 @@
       <c r="Y18" s="4">
         <v>125</v>
       </c>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="Z18" s="4">
+        <v>118</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>0</v>
+      </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>2075</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2660,14 +2736,18 @@
       <c r="Y19" s="4">
         <v>0</v>
       </c>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="Z19" s="4">
+        <v>108</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>151</v>
+      </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="9">
-        <v>1814</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2746,14 +2826,18 @@
       <c r="Y20" s="6">
         <v>1559</v>
       </c>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
+      <c r="Z20" s="6">
+        <v>1509</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>929</v>
+      </c>
       <c r="AB20" s="6"/>
       <c r="AC20" s="6"/>
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
       <c r="AF20" s="10">
-        <v>32879</v>
+        <v>35317</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2820,7 +2904,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.4867724867724865</v>
+        <v>3.7883597883597884</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D740AF2-B6E3-4B1A-B3F4-E52D036A760F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1025F7EB-0BE8-4469-B0A7-DB7FA69DF165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -574,16 +574,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>688</v>
+        <v>730</v>
       </c>
       <c r="C2" s="4">
-        <v>1279</v>
+        <v>1421</v>
       </c>
       <c r="D2" s="9">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" s="13">
-        <v>4.2857142857142856</v>
+        <v>4.4761904761904763</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -594,16 +594,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="C3" s="4">
-        <v>1645</v>
+        <v>1781</v>
       </c>
       <c r="D3" s="9">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E3" s="13">
-        <v>3.3809523809523809</v>
+        <v>3.5238095238095237</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -614,16 +614,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="C4" s="4">
-        <v>1511</v>
+        <v>1678</v>
       </c>
       <c r="D4" s="9">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" s="13">
-        <v>4.7619047619047619</v>
+        <v>4.7142857142857144</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -634,16 +634,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>392</v>
+        <v>439</v>
       </c>
       <c r="C5" s="4">
-        <v>1170</v>
+        <v>1312</v>
       </c>
       <c r="D5" s="9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E5" s="13">
-        <v>2.8571428571428572</v>
+        <v>3.0952380952380953</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -654,16 +654,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>554</v>
+        <v>607</v>
       </c>
       <c r="C6" s="4">
-        <v>1519</v>
+        <v>1675</v>
       </c>
       <c r="D6" s="9">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" s="13">
-        <v>4.2380952380952381</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -674,16 +674,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="C7" s="4">
-        <v>1684</v>
+        <v>1834</v>
       </c>
       <c r="D7" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="13">
-        <v>4.3809523809523814</v>
+        <v>4.4761904761904763</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -694,16 +694,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="C8" s="4">
-        <v>1435</v>
+        <v>1591</v>
       </c>
       <c r="D8" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="13">
-        <v>3.5238095238095237</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -714,16 +714,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>513</v>
+        <v>567</v>
       </c>
       <c r="C9" s="4">
-        <v>1622</v>
+        <v>1783</v>
       </c>
       <c r="D9" s="9">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" s="13">
-        <v>4.666666666666667</v>
+        <v>4.7619047619047619</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -734,16 +734,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="C10" s="4">
-        <v>1337</v>
+        <v>1459</v>
       </c>
       <c r="D10" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" s="13">
-        <v>3.5238095238095237</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -754,16 +754,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="C11" s="4">
-        <v>1576</v>
+        <v>1714</v>
       </c>
       <c r="D11" s="9">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E11" s="13">
-        <v>4.5714285714285712</v>
+        <v>4.9523809523809526</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -774,16 +774,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="C12" s="4">
-        <v>1324</v>
+        <v>1470</v>
       </c>
       <c r="D12" s="9">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E12" s="13">
-        <v>4.7619047619047619</v>
+        <v>5.0476190476190474</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -794,16 +794,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="C13" s="4">
-        <v>1462</v>
+        <v>1591</v>
       </c>
       <c r="D13" s="9">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E13" s="13">
-        <v>4.1428571428571432</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -814,16 +814,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="C14" s="4">
-        <v>1336</v>
+        <v>1488</v>
       </c>
       <c r="D14" s="9">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E14" s="13">
-        <v>3.3809523809523809</v>
+        <v>3.7142857142857144</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -834,16 +834,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="C15" s="4">
-        <v>1617</v>
+        <v>1751</v>
       </c>
       <c r="D15" s="9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="13">
-        <v>2.5238095238095237</v>
+        <v>2.5714285714285716</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -854,16 +854,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="C16" s="4">
-        <v>1470</v>
+        <v>1550</v>
       </c>
       <c r="D16" s="9">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E16" s="13">
-        <v>4.0952380952380949</v>
+        <v>4.2380952380952381</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -874,16 +874,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="C17" s="4">
-        <v>1565</v>
+        <v>1728</v>
       </c>
       <c r="D17" s="9">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E17" s="13">
-        <v>2.5238095238095237</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -894,16 +894,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C18" s="4">
-        <v>1644</v>
+        <v>1768</v>
       </c>
       <c r="D18" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E18" s="13">
-        <v>1.8571428571428572</v>
+        <v>1.9047619047619047</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -914,16 +914,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="C19" s="4">
-        <v>1543</v>
+        <v>1709</v>
       </c>
       <c r="D19" s="9">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E19" s="13">
-        <v>4.7142857142857144</v>
+        <v>4.8571428571428568</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="16"/>
@@ -933,16 +933,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>8578</v>
+        <v>9417</v>
       </c>
       <c r="C20" s="6">
-        <v>26739</v>
+        <v>29303</v>
       </c>
       <c r="D20" s="10">
-        <v>1432</v>
+        <v>1486</v>
       </c>
       <c r="E20" s="14">
-        <v>3.7883597883597884</v>
+        <v>3.9312169312169312</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="16"/>
@@ -1212,12 +1212,20 @@
       <c r="AA2" s="4">
         <v>0</v>
       </c>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>100</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>84</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
       <c r="AF2" s="9">
-        <v>1967</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1302,12 +1310,20 @@
       <c r="AA3" s="4">
         <v>110</v>
       </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>100</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>82</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>0</v>
+      </c>
       <c r="AF3" s="9">
-        <v>2067</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1392,12 +1408,20 @@
       <c r="AA4" s="4">
         <v>0</v>
       </c>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>96</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
       <c r="AF4" s="9">
-        <v>2087</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1482,12 +1506,20 @@
       <c r="AA5" s="4">
         <v>0</v>
       </c>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
+      <c r="AB5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>102</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>87</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>0</v>
+      </c>
       <c r="AF5" s="9">
-        <v>1562</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1495,16 +1527,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C6" s="4">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="D6" s="4">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="E6" s="4">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
@@ -1513,40 +1545,40 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
       </c>
       <c r="J6" s="4">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="K6" s="4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="L6" s="4">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="M6" s="4">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="N6" s="4">
         <v>0</v>
       </c>
       <c r="O6" s="4">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="P6" s="4">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q6" s="4">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="R6" s="4">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S6" s="4">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="T6" s="4">
         <v>0</v>
@@ -1555,29 +1587,37 @@
         <v>0</v>
       </c>
       <c r="V6" s="4">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="W6" s="4">
         <v>109</v>
       </c>
       <c r="X6" s="4">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y6" s="4">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="4">
+        <v>108</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>151</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
         <v>112</v>
       </c>
-      <c r="AA6" s="4">
-        <v>108</v>
-      </c>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
+      <c r="AD6" s="4">
+        <v>97</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
       <c r="AF6" s="9">
-        <v>1890</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1585,89 +1625,97 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C7" s="4">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>117</v>
+      </c>
+      <c r="F7" s="4">
+        <v>103</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>124</v>
+      </c>
+      <c r="I7" s="4">
+        <v>114</v>
+      </c>
+      <c r="J7" s="4">
+        <v>92</v>
+      </c>
+      <c r="K7" s="4">
+        <v>117</v>
+      </c>
+      <c r="L7" s="4">
+        <v>100</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>114</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>122</v>
+      </c>
+      <c r="R7" s="4">
+        <v>122</v>
+      </c>
+      <c r="S7" s="4">
+        <v>118</v>
+      </c>
+      <c r="T7" s="4">
         <v>111</v>
       </c>
-      <c r="E7" s="4">
-        <v>143</v>
-      </c>
-      <c r="F7" s="4">
-        <v>144</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>107</v>
-      </c>
-      <c r="I7" s="4">
-        <v>113</v>
-      </c>
-      <c r="J7" s="4">
-        <v>102</v>
-      </c>
-      <c r="K7" s="4">
-        <v>107</v>
-      </c>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>108</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <v>109</v>
-      </c>
-      <c r="P7" s="4">
-        <v>103</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>99</v>
-      </c>
-      <c r="R7" s="4">
-        <v>109</v>
-      </c>
-      <c r="S7" s="4">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>112</v>
-      </c>
       <c r="U7" s="4">
         <v>0</v>
       </c>
       <c r="V7" s="4">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="W7" s="4">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="X7" s="4">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="Y7" s="4">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="Z7" s="4">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="AA7" s="4">
         <v>0</v>
       </c>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>117</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>83</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
       <c r="AF7" s="9">
-        <v>2135</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1675,89 +1723,97 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E8" s="4">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F8" s="4">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="4">
+        <v>120</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>117</v>
+      </c>
+      <c r="M8" s="4">
+        <v>111</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>109</v>
+      </c>
+      <c r="R8" s="4">
+        <v>118</v>
+      </c>
+      <c r="S8" s="4">
+        <v>118</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>109</v>
+      </c>
+      <c r="W8" s="4">
+        <v>109</v>
+      </c>
+      <c r="X8" s="4">
+        <v>116</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>117</v>
+      </c>
+      <c r="Z8" s="4">
         <v>112</v>
       </c>
-      <c r="I8" s="4">
-        <v>96</v>
-      </c>
-      <c r="J8" s="4">
-        <v>80</v>
-      </c>
-      <c r="K8" s="4">
-        <v>112</v>
-      </c>
-      <c r="L8" s="4">
-        <v>91</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>131</v>
-      </c>
-      <c r="R8" s="4">
-        <v>106</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
-        <v>159</v>
-      </c>
-      <c r="U8" s="4">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4">
-        <v>98</v>
-      </c>
-      <c r="W8" s="4">
-        <v>125</v>
-      </c>
-      <c r="X8" s="4">
-        <v>122</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>111</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>105</v>
-      </c>
       <c r="AA8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
       <c r="AF8" s="9">
-        <v>1813</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1765,89 +1821,97 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D9" s="4">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="E9" s="4">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F9" s="4">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="4">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="J9" s="4">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K9" s="4">
+        <v>107</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>108</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>109</v>
+      </c>
+      <c r="P9" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>99</v>
+      </c>
+      <c r="R9" s="4">
+        <v>109</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>112</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <v>96</v>
+      </c>
+      <c r="W9" s="4">
+        <v>106</v>
+      </c>
+      <c r="X9" s="4">
+        <v>111</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>112</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4">
         <v>115</v>
       </c>
-      <c r="L9" s="4">
-        <v>110</v>
-      </c>
-      <c r="M9" s="4">
-        <v>106</v>
-      </c>
-      <c r="N9" s="4">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
-        <v>110</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>97</v>
-      </c>
-      <c r="R9" s="4">
-        <v>111</v>
-      </c>
-      <c r="S9" s="4">
-        <v>94</v>
-      </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4">
-        <v>106</v>
-      </c>
-      <c r="W9" s="4">
-        <v>112</v>
-      </c>
-      <c r="X9" s="4">
-        <v>108</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>117</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="4">
-        <v>114</v>
-      </c>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
-      <c r="AE9" s="4"/>
+      <c r="AD9" s="4">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>0</v>
+      </c>
       <c r="AF9" s="9">
-        <v>2025</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1855,89 +1919,97 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>137</v>
+      </c>
+      <c r="F10" s="4">
+        <v>138</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>112</v>
+      </c>
+      <c r="I10" s="4">
+        <v>96</v>
+      </c>
+      <c r="J10" s="4">
+        <v>80</v>
+      </c>
+      <c r="K10" s="4">
+        <v>112</v>
+      </c>
+      <c r="L10" s="4">
+        <v>91</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4">
+        <v>90</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>131</v>
+      </c>
+      <c r="R10" s="4">
+        <v>106</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>159</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>98</v>
+      </c>
+      <c r="W10" s="4">
+        <v>125</v>
+      </c>
+      <c r="X10" s="4">
+        <v>122</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>111</v>
+      </c>
+      <c r="Z10" s="4">
         <v>105</v>
       </c>
-      <c r="C10" s="4">
-        <v>126</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>144</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>110</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4">
-        <v>109</v>
-      </c>
-      <c r="L10" s="4">
-        <v>108</v>
-      </c>
-      <c r="M10" s="4">
-        <v>104</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4">
-        <v>104</v>
-      </c>
-      <c r="P10" s="4">
-        <v>117</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>110</v>
-      </c>
-      <c r="R10" s="4">
-        <v>120</v>
-      </c>
-      <c r="S10" s="4">
-        <v>106</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4">
-        <v>108</v>
-      </c>
-      <c r="W10" s="4">
-        <v>103</v>
-      </c>
-      <c r="X10" s="4">
-        <v>106</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>114</v>
-      </c>
       <c r="AA10" s="4">
-        <v>107</v>
-      </c>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>105</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>80</v>
+      </c>
+      <c r="AE10" s="4">
+        <v>0</v>
+      </c>
       <c r="AF10" s="9">
-        <v>1901</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1945,89 +2017,97 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
+        <v>117</v>
+      </c>
+      <c r="C11" s="4">
+        <v>136</v>
+      </c>
+      <c r="D11" s="4">
+        <v>130</v>
+      </c>
+      <c r="E11" s="4">
+        <v>132</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>106</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>104</v>
+      </c>
+      <c r="K11" s="4">
         <v>115</v>
       </c>
-      <c r="C11" s="4">
-        <v>101</v>
-      </c>
-      <c r="D11" s="4">
-        <v>102</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>76</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>106</v>
-      </c>
-      <c r="I11" s="4">
-        <v>87</v>
-      </c>
-      <c r="J11" s="4">
-        <v>73</v>
-      </c>
-      <c r="K11" s="4">
-        <v>113</v>
-      </c>
       <c r="L11" s="4">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="M11" s="4">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N11" s="4">
         <v>0</v>
       </c>
       <c r="O11" s="4">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="P11" s="4">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Q11" s="4">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="R11" s="4">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="S11" s="4">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="T11" s="4">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="U11" s="4">
         <v>0</v>
       </c>
       <c r="V11" s="4">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="W11" s="4">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="X11" s="4">
         <v>108</v>
       </c>
       <c r="Y11" s="4">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="Z11" s="4">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>114</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>87</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>0</v>
+      </c>
       <c r="AF11" s="9">
-        <v>1906</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2038,86 +2118,94 @@
         <v>105</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
         <v>110</v>
       </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>98</v>
-      </c>
-      <c r="I12" s="4">
-        <v>97</v>
-      </c>
       <c r="J12" s="4">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L12" s="4">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M12" s="4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N12" s="4">
         <v>0</v>
       </c>
       <c r="O12" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P12" s="4">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q12" s="4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="R12" s="4">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="S12" s="4">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="T12" s="4">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="U12" s="4">
         <v>0</v>
       </c>
       <c r="V12" s="4">
+        <v>108</v>
+      </c>
+      <c r="W12" s="4">
+        <v>103</v>
+      </c>
+      <c r="X12" s="4">
+        <v>106</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>114</v>
+      </c>
+      <c r="AA12" s="4">
         <v>107</v>
       </c>
-      <c r="W12" s="4">
-        <v>96</v>
-      </c>
-      <c r="X12" s="4">
-        <v>122</v>
-      </c>
-      <c r="Y12" s="4">
-        <v>111</v>
-      </c>
-      <c r="Z12" s="4">
-        <v>105</v>
-      </c>
-      <c r="AA12" s="4">
-        <v>3</v>
-      </c>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>103</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>0</v>
+      </c>
       <c r="AF12" s="9">
-        <v>1774</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2125,89 +2213,97 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C13" s="4">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D13" s="4">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E13" s="4">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="I13" s="4">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="J13" s="4">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="K13" s="4">
+        <v>113</v>
+      </c>
+      <c r="L13" s="4">
         <v>93</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>114</v>
+      </c>
+      <c r="P13" s="4">
+        <v>95</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>110</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4">
+        <v>109</v>
+      </c>
+      <c r="T13" s="4">
+        <v>108</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
         <v>94</v>
       </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4">
+      <c r="W13" s="4">
+        <v>96</v>
+      </c>
+      <c r="X13" s="4">
+        <v>108</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>100</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>106</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>107</v>
+      </c>
+      <c r="AD13" s="4">
         <v>68</v>
       </c>
-      <c r="P13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>102</v>
-      </c>
-      <c r="R13" s="4">
-        <v>125</v>
-      </c>
-      <c r="S13" s="4">
-        <v>101</v>
-      </c>
-      <c r="T13" s="4">
-        <v>115</v>
-      </c>
-      <c r="U13" s="4">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4">
-        <v>105</v>
-      </c>
-      <c r="W13" s="4">
-        <v>103</v>
-      </c>
-      <c r="X13" s="4">
-        <v>110</v>
-      </c>
-      <c r="Y13" s="4">
-        <v>101</v>
-      </c>
-      <c r="Z13" s="4">
-        <v>102</v>
-      </c>
-      <c r="AA13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
+      <c r="AE13" s="4">
+        <v>0</v>
+      </c>
       <c r="AF13" s="9">
-        <v>1970</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2215,89 +2311,97 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
+        <v>105</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>111</v>
+      </c>
+      <c r="F14" s="4">
+        <v>110</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>98</v>
+      </c>
+      <c r="I14" s="4">
+        <v>97</v>
+      </c>
+      <c r="J14" s="4">
+        <v>86</v>
+      </c>
+      <c r="K14" s="4">
+        <v>106</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>106</v>
+      </c>
+      <c r="P14" s="4">
+        <v>113</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>126</v>
+      </c>
+      <c r="S14" s="4">
+        <v>59</v>
+      </c>
+      <c r="T14" s="4">
+        <v>113</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
         <v>107</v>
       </c>
-      <c r="C14" s="4">
-        <v>133</v>
-      </c>
-      <c r="D14" s="4">
-        <v>124</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>139</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>104</v>
-      </c>
-      <c r="I14" s="4">
-        <v>114</v>
-      </c>
-      <c r="J14" s="4">
-        <v>107</v>
-      </c>
-      <c r="K14" s="4">
-        <v>106</v>
-      </c>
-      <c r="L14" s="4">
-        <v>104</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4">
-        <v>104</v>
-      </c>
-      <c r="P14" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>103</v>
-      </c>
-      <c r="R14" s="4">
-        <v>112</v>
-      </c>
-      <c r="S14" s="4">
-        <v>100</v>
-      </c>
-      <c r="T14" s="4">
-        <v>115</v>
-      </c>
-      <c r="U14" s="4">
-        <v>0</v>
-      </c>
-      <c r="V14" s="4">
-        <v>109</v>
-      </c>
       <c r="W14" s="4">
+        <v>96</v>
+      </c>
+      <c r="X14" s="4">
+        <v>122</v>
+      </c>
+      <c r="Y14" s="4">
         <v>111</v>
       </c>
-      <c r="X14" s="4">
-        <v>111</v>
-      </c>
-      <c r="Y14" s="4">
-        <v>102</v>
-      </c>
       <c r="Z14" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AA14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>108</v>
+      </c>
+      <c r="AD14" s="4">
+        <v>84</v>
+      </c>
+      <c r="AE14" s="4">
+        <v>0</v>
+      </c>
       <c r="AF14" s="9">
-        <v>2109</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2305,89 +2409,97 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
+        <v>104</v>
+      </c>
+      <c r="C15" s="4">
+        <v>112</v>
+      </c>
+      <c r="D15" s="4">
         <v>111</v>
       </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
-        <v>126</v>
-      </c>
       <c r="E15" s="4">
+        <v>121</v>
+      </c>
+      <c r="F15" s="4">
+        <v>102</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>99</v>
+      </c>
+      <c r="J15" s="4">
+        <v>102</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93</v>
+      </c>
+      <c r="L15" s="4">
+        <v>94</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>68</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>102</v>
+      </c>
+      <c r="R15" s="4">
+        <v>125</v>
+      </c>
+      <c r="S15" s="4">
+        <v>101</v>
+      </c>
+      <c r="T15" s="4">
+        <v>115</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
         <v>105</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="W15" s="4">
+        <v>103</v>
+      </c>
+      <c r="X15" s="4">
+        <v>110</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>101</v>
+      </c>
+      <c r="Z15" s="4">
         <v>102</v>
       </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
+      <c r="AA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
         <v>103</v>
       </c>
-      <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4">
-        <v>102</v>
-      </c>
-      <c r="M15" s="4">
-        <v>106</v>
-      </c>
-      <c r="N15" s="4">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4">
-        <v>107</v>
-      </c>
-      <c r="P15" s="4">
-        <v>103</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>105</v>
-      </c>
-      <c r="R15" s="4">
-        <v>138</v>
-      </c>
-      <c r="S15" s="4">
-        <v>114</v>
-      </c>
-      <c r="T15" s="4">
-        <v>0</v>
-      </c>
-      <c r="U15" s="4">
-        <v>0</v>
-      </c>
-      <c r="V15" s="4">
-        <v>111</v>
-      </c>
-      <c r="W15" s="4">
-        <v>111</v>
-      </c>
-      <c r="X15" s="4">
-        <v>101</v>
-      </c>
-      <c r="Y15" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="4">
-        <v>111</v>
-      </c>
-      <c r="AA15" s="4">
-        <v>110</v>
-      </c>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
+      <c r="AD15" s="4">
+        <v>73</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
       <c r="AF15" s="9">
-        <v>1866</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2395,89 +2507,97 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C16" s="4">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D16" s="4">
+        <v>123</v>
+      </c>
+      <c r="E16" s="4">
+        <v>120</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>126</v>
+      </c>
+      <c r="I16" s="4">
+        <v>106</v>
+      </c>
+      <c r="J16" s="4">
+        <v>115</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>108</v>
+      </c>
+      <c r="M16" s="4">
+        <v>110</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>116</v>
+      </c>
+      <c r="P16" s="4">
+        <v>121</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>107</v>
+      </c>
+      <c r="R16" s="4">
+        <v>106</v>
+      </c>
+      <c r="S16" s="4">
+        <v>121</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>114</v>
+      </c>
+      <c r="W16" s="4">
         <v>111</v>
       </c>
-      <c r="E16" s="4">
-        <v>107</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4">
-        <v>98</v>
-      </c>
-      <c r="I16" s="4">
-        <v>104</v>
-      </c>
-      <c r="J16" s="4">
-        <v>102</v>
-      </c>
-      <c r="K16" s="4">
-        <v>103</v>
-      </c>
-      <c r="L16" s="4">
-        <v>102</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
-        <v>106</v>
-      </c>
-      <c r="P16" s="4">
-        <v>99</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>106</v>
-      </c>
-      <c r="R16" s="4">
-        <v>129</v>
-      </c>
-      <c r="S16" s="4">
-        <v>113</v>
-      </c>
-      <c r="T16" s="4">
-        <v>0</v>
-      </c>
-      <c r="U16" s="4">
-        <v>0</v>
-      </c>
-      <c r="V16" s="4">
-        <v>0</v>
-      </c>
-      <c r="W16" s="4">
-        <v>105</v>
-      </c>
       <c r="X16" s="4">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="Y16" s="4">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="Z16" s="4">
         <v>0</v>
       </c>
       <c r="AA16" s="4">
-        <v>115</v>
-      </c>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>117</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
       <c r="AF16" s="9">
-        <v>1934</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2485,89 +2605,97 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="C17" s="4">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="D17" s="4">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E17" s="4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I17" s="4">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J17" s="4">
+        <v>107</v>
+      </c>
+      <c r="K17" s="4">
+        <v>106</v>
+      </c>
+      <c r="L17" s="4">
+        <v>104</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>104</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>103</v>
+      </c>
+      <c r="R17" s="4">
+        <v>112</v>
+      </c>
+      <c r="S17" s="4">
+        <v>100</v>
+      </c>
+      <c r="T17" s="4">
         <v>115</v>
       </c>
-      <c r="K17" s="4">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
-        <v>108</v>
-      </c>
-      <c r="M17" s="4">
-        <v>110</v>
-      </c>
-      <c r="N17" s="4">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4">
-        <v>116</v>
-      </c>
-      <c r="P17" s="4">
-        <v>121</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>107</v>
-      </c>
-      <c r="R17" s="4">
-        <v>106</v>
-      </c>
-      <c r="S17" s="4">
-        <v>121</v>
-      </c>
-      <c r="T17" s="4">
-        <v>0</v>
-      </c>
       <c r="U17" s="4">
         <v>0</v>
       </c>
       <c r="V17" s="4">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="W17" s="4">
         <v>111</v>
       </c>
       <c r="X17" s="4">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Y17" s="4">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="Z17" s="4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AA17" s="4">
-        <v>111</v>
-      </c>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>105</v>
+      </c>
+      <c r="AD17" s="4">
+        <v>106</v>
+      </c>
+      <c r="AE17" s="4">
+        <v>0</v>
+      </c>
       <c r="AF17" s="9">
-        <v>2045</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2575,89 +2703,97 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
+        <v>111</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>126</v>
+      </c>
+      <c r="E18" s="4">
+        <v>105</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
         <v>102</v>
       </c>
-      <c r="C18" s="4">
-        <v>116</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>117</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
         <v>103</v>
       </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4">
-        <v>124</v>
-      </c>
-      <c r="I18" s="4">
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>102</v>
+      </c>
+      <c r="M18" s="4">
+        <v>106</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>107</v>
+      </c>
+      <c r="P18" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>105</v>
+      </c>
+      <c r="R18" s="4">
+        <v>138</v>
+      </c>
+      <c r="S18" s="4">
         <v>114</v>
       </c>
-      <c r="J18" s="4">
-        <v>92</v>
-      </c>
-      <c r="K18" s="4">
-        <v>117</v>
-      </c>
-      <c r="L18" s="4">
-        <v>100</v>
-      </c>
-      <c r="M18" s="4">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4">
-        <v>0</v>
-      </c>
-      <c r="O18" s="4">
-        <v>114</v>
-      </c>
-      <c r="P18" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="4">
-        <v>122</v>
-      </c>
-      <c r="R18" s="4">
-        <v>122</v>
-      </c>
-      <c r="S18" s="4">
-        <v>118</v>
-      </c>
       <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
         <v>111</v>
       </c>
-      <c r="U18" s="4">
-        <v>0</v>
-      </c>
-      <c r="V18" s="4">
-        <v>127</v>
-      </c>
       <c r="W18" s="4">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="X18" s="4">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="Y18" s="4">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="4">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>105</v>
+      </c>
+      <c r="AD18" s="4">
+        <v>46</v>
+      </c>
+      <c r="AE18" s="4">
+        <v>0</v>
+      </c>
       <c r="AF18" s="9">
-        <v>2193</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2665,16 +2801,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C19" s="4">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D19" s="4">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E19" s="4">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
@@ -2683,71 +2819,79 @@
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="I19" s="4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="J19" s="4">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K19" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L19" s="4">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="M19" s="4">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N19" s="4">
         <v>0</v>
       </c>
       <c r="O19" s="4">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P19" s="4">
         <v>99</v>
       </c>
       <c r="Q19" s="4">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="R19" s="4">
+        <v>129</v>
+      </c>
+      <c r="S19" s="4">
+        <v>113</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
         <v>105</v>
       </c>
-      <c r="S19" s="4">
+      <c r="X19" s="4">
         <v>112</v>
       </c>
-      <c r="T19" s="4">
-        <v>0</v>
-      </c>
-      <c r="U19" s="4">
-        <v>0</v>
-      </c>
-      <c r="V19" s="4">
-        <v>106</v>
-      </c>
-      <c r="W19" s="4">
-        <v>109</v>
-      </c>
-      <c r="X19" s="4">
+      <c r="Y19" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="4">
         <v>115</v>
       </c>
-      <c r="Y19" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="4">
-        <v>108</v>
-      </c>
-      <c r="AA19" s="4">
-        <v>151</v>
-      </c>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
+      <c r="AB19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="4">
+        <v>95</v>
+      </c>
+      <c r="AD19" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE19" s="4">
+        <v>0</v>
+      </c>
       <c r="AF19" s="9">
-        <v>2073</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2832,12 +2976,20 @@
       <c r="AA20" s="6">
         <v>929</v>
       </c>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6"/>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="6"/>
+      <c r="AB20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="6">
+        <v>1806</v>
+      </c>
+      <c r="AD20" s="6">
+        <v>1597</v>
+      </c>
+      <c r="AE20" s="6">
+        <v>0</v>
+      </c>
       <c r="AF20" s="10">
-        <v>35317</v>
+        <v>38720</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2904,7 +3056,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.7883597883597884</v>
+        <v>3.9312169312169312</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1025F7EB-0BE8-4469-B0A7-DB7FA69DF165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F3EEF1-C8F2-481B-A0BE-D50B7B34F19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -574,16 +574,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="C2" s="4">
-        <v>1421</v>
+        <v>1503</v>
       </c>
       <c r="D2" s="9">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E2" s="13">
-        <v>4.4761904761904763</v>
+        <v>4.4090909090909092</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -594,16 +594,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="C3" s="4">
-        <v>1781</v>
+        <v>1873</v>
       </c>
       <c r="D3" s="9">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="13">
-        <v>3.5238095238095237</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -614,16 +614,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="C4" s="4">
-        <v>1678</v>
+        <v>1766</v>
       </c>
       <c r="D4" s="9">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E4" s="13">
-        <v>4.7142857142857144</v>
+        <v>4.8636363636363633</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -634,16 +634,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="C5" s="4">
-        <v>1312</v>
+        <v>1398</v>
       </c>
       <c r="D5" s="9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E5" s="13">
-        <v>3.0952380952380953</v>
+        <v>3.1818181818181817</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -654,16 +654,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>607</v>
+        <v>643</v>
       </c>
       <c r="C6" s="4">
-        <v>1675</v>
+        <v>1746</v>
       </c>
       <c r="D6" s="9">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E6" s="13">
-        <v>4.333333333333333</v>
+        <v>4.3636363636363633</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -674,16 +674,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="C7" s="4">
-        <v>1834</v>
+        <v>1928</v>
       </c>
       <c r="D7" s="9">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" s="13">
-        <v>4.4761904761904763</v>
+        <v>4.4090909090909092</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -694,16 +694,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="C8" s="4">
-        <v>1591</v>
+        <v>1678</v>
       </c>
       <c r="D8" s="9">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E8" s="13">
-        <v>3.5714285714285716</v>
+        <v>3.6818181818181817</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -714,16 +714,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="C9" s="4">
-        <v>1783</v>
+        <v>1875</v>
       </c>
       <c r="D9" s="9">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E9" s="13">
-        <v>4.7619047619047619</v>
+        <v>4.8636363636363633</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -734,16 +734,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="C10" s="4">
-        <v>1459</v>
+        <v>1531</v>
       </c>
       <c r="D10" s="9">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="13">
-        <v>3.5714285714285716</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -754,16 +754,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C11" s="4">
-        <v>1714</v>
+        <v>1808</v>
       </c>
       <c r="D11" s="9">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" s="13">
-        <v>4.9523809523809526</v>
+        <v>4.7727272727272725</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -774,16 +774,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>640</v>
+        <v>671</v>
       </c>
       <c r="C12" s="4">
-        <v>1470</v>
+        <v>1543</v>
       </c>
       <c r="D12" s="9">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="E12" s="13">
-        <v>5.0476190476190474</v>
+        <v>5.5</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -794,16 +794,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="C13" s="4">
-        <v>1591</v>
+        <v>1667</v>
       </c>
       <c r="D13" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E13" s="13">
-        <v>4.2857142857142856</v>
+        <v>4.3181818181818183</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -814,16 +814,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="C14" s="4">
-        <v>1488</v>
+        <v>1576</v>
       </c>
       <c r="D14" s="9">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E14" s="13">
-        <v>3.7142857142857144</v>
+        <v>3.6818181818181817</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -834,16 +834,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C15" s="4">
-        <v>1751</v>
+        <v>1845</v>
       </c>
       <c r="D15" s="9">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E15" s="13">
-        <v>2.5714285714285716</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -854,16 +854,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="C16" s="4">
-        <v>1550</v>
+        <v>1636</v>
       </c>
       <c r="D16" s="9">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E16" s="13">
-        <v>4.2380952380952381</v>
+        <v>4.2727272727272725</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -874,16 +874,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="C17" s="4">
-        <v>1728</v>
+        <v>1810</v>
       </c>
       <c r="D17" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="13">
-        <v>2.6666666666666665</v>
+        <v>2.5909090909090908</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -894,16 +894,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C18" s="4">
-        <v>1768</v>
+        <v>1864</v>
       </c>
       <c r="D18" s="9">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E18" s="13">
-        <v>1.9047619047619047</v>
+        <v>2.0909090909090908</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -914,16 +914,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="C19" s="4">
-        <v>1709</v>
+        <v>1804</v>
       </c>
       <c r="D19" s="9">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E19" s="13">
-        <v>4.8571428571428568</v>
+        <v>4.8181818181818183</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="16"/>
@@ -933,16 +933,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>9417</v>
+        <v>9781</v>
       </c>
       <c r="C20" s="6">
-        <v>29303</v>
+        <v>30851</v>
       </c>
       <c r="D20" s="10">
-        <v>1486</v>
+        <v>1570</v>
       </c>
       <c r="E20" s="14">
-        <v>3.9312169312169312</v>
+        <v>3.9646464646464645</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="16"/>
@@ -1222,10 +1222,10 @@
         <v>84</v>
       </c>
       <c r="AE2" s="4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AF2" s="9">
-        <v>2151</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1320,10 +1320,10 @@
         <v>82</v>
       </c>
       <c r="AE3" s="4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AF3" s="9">
-        <v>2249</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1418,10 +1418,10 @@
         <v>96</v>
       </c>
       <c r="AE4" s="4">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AF4" s="9">
-        <v>2289</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1516,10 +1516,10 @@
         <v>87</v>
       </c>
       <c r="AE5" s="4">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AF5" s="9">
-        <v>1751</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1614,10 +1614,10 @@
         <v>97</v>
       </c>
       <c r="AE6" s="4">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AF6" s="9">
-        <v>2282</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1712,10 +1712,10 @@
         <v>83</v>
       </c>
       <c r="AE7" s="4">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AF7" s="9">
-        <v>2393</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1810,10 +1810,10 @@
         <v>100</v>
       </c>
       <c r="AE8" s="4">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AF8" s="9">
-        <v>2096</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1908,10 +1908,10 @@
         <v>100</v>
       </c>
       <c r="AE9" s="4">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AF9" s="9">
-        <v>2350</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -2006,10 +2006,10 @@
         <v>80</v>
       </c>
       <c r="AE10" s="4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF10" s="9">
-        <v>1998</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -2104,10 +2104,10 @@
         <v>87</v>
       </c>
       <c r="AE11" s="4">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AF11" s="9">
-        <v>2226</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2202,10 +2202,10 @@
         <v>103</v>
       </c>
       <c r="AE12" s="4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AF12" s="9">
-        <v>2110</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -2300,10 +2300,10 @@
         <v>68</v>
       </c>
       <c r="AE13" s="4">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AF13" s="9">
-        <v>2081</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2398,10 +2398,10 @@
         <v>84</v>
       </c>
       <c r="AE14" s="4">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AF14" s="9">
-        <v>1966</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -2496,10 +2496,10 @@
         <v>73</v>
       </c>
       <c r="AE15" s="4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AF15" s="9">
-        <v>2146</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2594,10 +2594,10 @@
         <v>117</v>
       </c>
       <c r="AE16" s="4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF16" s="9">
-        <v>2162</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -2692,10 +2692,10 @@
         <v>106</v>
       </c>
       <c r="AE17" s="4">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AF17" s="9">
-        <v>2320</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -2790,10 +2790,10 @@
         <v>46</v>
       </c>
       <c r="AE18" s="4">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AF18" s="9">
-        <v>2017</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2888,10 +2888,10 @@
         <v>104</v>
       </c>
       <c r="AE19" s="4">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AF19" s="9">
-        <v>2133</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2986,10 +2986,10 @@
         <v>1597</v>
       </c>
       <c r="AE20" s="6">
-        <v>0</v>
+        <v>1912</v>
       </c>
       <c r="AF20" s="10">
-        <v>38720</v>
+        <v>40632</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.9312169312169312</v>
+        <v>3.9646464646464645</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F3EEF1-C8F2-481B-A0BE-D50B7B34F19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45839DD2-3228-4C1B-8216-55D7C4002ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,16 +734,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C10" s="4">
         <v>1531</v>
       </c>
       <c r="D10" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -939,10 +939,10 @@
         <v>30851</v>
       </c>
       <c r="D20" s="10">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E20" s="14">
-        <v>3.9646464646464645</v>
+        <v>3.9671717171717171</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="16"/>
@@ -1985,7 +1985,7 @@
         <v>125</v>
       </c>
       <c r="X10" s="4">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y10" s="4">
         <v>111</v>
@@ -2009,7 +2009,7 @@
         <v>95</v>
       </c>
       <c r="AF10" s="9">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -2965,7 +2965,7 @@
         <v>1823</v>
       </c>
       <c r="X20" s="6">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="Y20" s="6">
         <v>1559</v>
@@ -2989,7 +2989,7 @@
         <v>1912</v>
       </c>
       <c r="AF20" s="10">
-        <v>40632</v>
+        <v>40633</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.9646464646464645</v>
+        <v>3.9671717171717171</v>
       </c>
       <c r="D2" s="1"/>
     </row>
